--- a/output/laminas_provinciales/prov_i_ingr_median_a_2024_aysen.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_median_a_2024_aysen.xlsx
@@ -74,7 +74,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 11:11</t>
+    <t xml:space="preserve">2026-09-09 22:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/laminas_provinciales/prov_i_ingr_median_a_2024_aysen.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_median_a_2024_aysen.xlsx
@@ -74,7 +74,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:08</t>
+    <t xml:space="preserve">2026-09-17 13:38</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -955,26 +955,26 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>938030</v>
+        <v>960038</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>955270</v>
+        <v>938030</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>960038</v>
+        <v>955270</v>
       </c>
     </row>
     <row r="5">
@@ -1015,101 +1015,101 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>776830</v>
+        <v>791860</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>884020</v>
+        <v>889081</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>938030</v>
+        <v>960038</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>785163</v>
+        <v>776830</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>913439</v>
+        <v>884020</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>955270</v>
+        <v>938030</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>791860</v>
+        <v>785163</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>889081</v>
+        <v>913439</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>960038</v>
+        <v>955270</v>
       </c>
     </row>
     <row r="11">

--- a/output/laminas_provinciales/prov_i_ingr_median_a_2024_aysen.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_median_a_2024_aysen.xlsx
@@ -74,7 +74,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 13:38</t>
+    <t xml:space="preserve">2026-09-25 21:33</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/laminas_provinciales/prov_i_ingr_median_a_2024_aysen.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_median_a_2024_aysen.xlsx
@@ -55,7 +55,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-28 21:38</t>
+    <t xml:space="preserve">2026-10-05 07:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -485,7 +485,7 @@
         <v>5</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>948370</v>
+        <v>948371</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>882470</v>
@@ -699,7 +699,7 @@
         <v>7</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>974672</v>
+        <v>974673</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>945000</v>
